--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487640_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487640_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.417</v>
+        <v>7.2718</v>
       </c>
       <c r="E2" t="n">
-        <v>6.6196</v>
+        <v>6.7197</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7974</v>
+        <v>0.5521</v>
       </c>
       <c r="G2" t="n">
         <v>5.8465</v>
@@ -610,13 +610,13 @@
         <v>1.1642</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6002999999999999</v>
+        <v>0.4551</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1806</v>
+        <v>-0.0805</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7809</v>
+        <v>0.5356</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4978</v>
+        <v>1.9155</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6138</v>
+        <v>1.1133</v>
       </c>
       <c r="F3" t="n">
-        <v>0.884</v>
+        <v>0.8022</v>
       </c>
       <c r="G3" t="n">
         <v>0.4056</v>
@@ -688,13 +688,13 @@
         <v>0.9702</v>
       </c>
       <c r="S3" t="n">
-        <v>1.316</v>
+        <v>0.7338</v>
       </c>
       <c r="T3" t="n">
-        <v>0.729</v>
+        <v>0.2285</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5871</v>
+        <v>0.5053</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. DIALLO</t>
+          <t>B. OJEDA OCHOA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.8804</v>
+        <v>-1.0922</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1611</v>
+        <v>-1.6626</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.0414</v>
+        <v>0.5704</v>
       </c>
       <c r="G4" t="n">
-        <v>-3.2016</v>
+        <v>-1.2974</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.2012</v>
+        <v>-0.7118</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.0004</v>
+        <v>-0.5856</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.569</v>
+        <v>-0.7446</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.6096</v>
+        <v>-0.1812</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0406</v>
+        <v>-0.5633</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.6325</v>
+        <v>-0.5528999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5916</v>
+        <v>-0.5306</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.041</v>
+        <v>-0.0223</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.3881</v>
+        <v>-1.1642</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9702</v>
+        <v>-2.1344</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5821</v>
+        <v>0.9702</v>
       </c>
       <c r="S4" t="n">
-        <v>2.0018</v>
+        <v>0.4276</v>
       </c>
       <c r="T4" t="n">
-        <v>1.7003</v>
+        <v>-0.0076</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3015</v>
+        <v>0.4352</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7075</v>
+        <v>0.9418</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="X4" t="n">
-        <v>0.7075</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. OJEDA OCHOA</t>
+          <t>M. DIALLO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.2112</v>
+        <v>-2.2451</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.5635</v>
+        <v>-1.0401</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3524</v>
+        <v>-1.205</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.2974</v>
+        <v>-3.2016</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7118</v>
+        <v>-1.2012</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5856</v>
+        <v>-2.0004</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.7446</v>
+        <v>-0.569</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.1812</v>
+        <v>-0.6096</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5633</v>
+        <v>0.0406</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5528999999999999</v>
+        <v>-2.6325</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5306</v>
+        <v>-0.5916</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0223</v>
+        <v>-2.041</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.1642</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.1344</v>
+        <v>-0.9702</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9702</v>
+        <v>0.5821</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6913</v>
+        <v>0.637</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9085</v>
+        <v>0.4991</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2172</v>
+        <v>0.138</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9418</v>
+        <v>0.7075</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2821</v>
+        <v>0.7075</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-4.0851</v>
+        <v>-3.9577</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.4041</v>
+        <v>-2.304</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.6809</v>
+        <v>-1.6537</v>
       </c>
       <c r="G6" t="n">
         <v>-3.4331</v>
@@ -922,13 +922,13 @@
         <v>0.194</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5639</v>
+        <v>-0.4366</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4845</v>
+        <v>-0.3844</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0794</v>
+        <v>-0.0521</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2821</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-4.8874</v>
+        <v>-4.8606</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.0156</v>
+        <v>-3.3159</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.8718</v>
+        <v>-1.5447</v>
       </c>
       <c r="G7" t="n">
         <v>-3.3598</v>
@@ -1000,13 +1000,13 @@
         <v>1.1642</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6052</v>
+        <v>-0.5785</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0584</v>
+        <v>-0.3587</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5469000000000001</v>
+        <v>-0.2198</v>
       </c>
       <c r="V7" t="n">
         <v>0.0478</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. CALVO SALVE</t>
+          <t>L. VALERA VILLEGAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.4489</v>
+        <v>-5.1001</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.1128</v>
+        <v>-4.6948</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.3361</v>
+        <v>-0.4053</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.9826</v>
+        <v>-2.6596</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.194</v>
+        <v>0.5948</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7886</v>
+        <v>-3.2544</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1898</v>
+        <v>-1.2947</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5232</v>
+        <v>0.725</v>
       </c>
       <c r="L8" t="n">
-        <v>0.713</v>
+        <v>-2.0198</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.1724</v>
+        <v>-1.3648</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.6708</v>
+        <v>-0.1302</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.5015</v>
+        <v>-1.2346</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9403</v>
+        <v>-2.9105</v>
       </c>
       <c r="R8" t="n">
         <v>0.9702</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2723</v>
+        <v>-0.5002</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3623</v>
+        <v>-0.4896</v>
       </c>
       <c r="U8" t="n">
-        <v>0.09</v>
+        <v>-0.0106</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. VALERA VILLEGAS</t>
+          <t>E. CALVO SALVE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.8915</v>
+        <v>-5.3216</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.2954</v>
+        <v>-2.0127</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5961</v>
+        <v>-3.3089</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.6596</v>
+        <v>-2.9826</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5948</v>
+        <v>-2.194</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.2544</v>
+        <v>-0.7886</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.2947</v>
+        <v>0.1898</v>
       </c>
       <c r="K9" t="n">
-        <v>0.725</v>
+        <v>-0.5232</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.0198</v>
+        <v>0.713</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3648</v>
+        <v>-3.1724</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1302</v>
+        <v>-1.6708</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.2346</v>
+        <v>-1.5015</v>
       </c>
       <c r="P9" t="n">
+        <v>-0.9702</v>
+      </c>
+      <c r="Q9" t="n">
         <v>-1.9403</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>-2.9105</v>
       </c>
       <c r="R9" t="n">
         <v>0.9702</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.2916</v>
+        <v>-0.145</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0902</v>
+        <v>-0.2622</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2014</v>
+        <v>0.1172</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.9274</v>
+        <v>-8.026999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>-7.5032</v>
+        <v>-7.303</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4242</v>
+        <v>-0.724</v>
       </c>
       <c r="G10" t="n">
         <v>-6.8378</v>
@@ -1234,13 +1234,13 @@
         <v>0.7761</v>
       </c>
       <c r="S10" t="n">
-        <v>0.297</v>
+        <v>0.1974</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4834</v>
+        <v>-0.2832</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7804</v>
+        <v>0.4806</v>
       </c>
       <c r="V10" t="n">
         <v>0.9418</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-21.4171</v>
+        <v>-21.417</v>
       </c>
       <c r="E11" t="n">
         <v>-14.5001</v>
       </c>
       <c r="F11" t="n">
-        <v>-6.9167</v>
+        <v>-6.9169</v>
       </c>
       <c r="G11" t="n">
         <v>-17.5198</v>
@@ -1312,7 +1312,7 @@
         <v>7.761399999999998</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7908000000000002</v>
+        <v>0.7906</v>
       </c>
       <c r="T11" t="n">
         <v>-1.1386</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.536</v>
+        <v>5.7179</v>
       </c>
       <c r="E12" t="n">
-        <v>3.0525</v>
+        <v>3.1526</v>
       </c>
       <c r="F12" t="n">
-        <v>2.4835</v>
+        <v>2.5653</v>
       </c>
       <c r="G12" t="n">
         <v>4.0523</v>
@@ -1390,13 +1390,13 @@
         <v>2.1344</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.079</v>
+        <v>0.1029</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2412</v>
+        <v>-0.1411</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1622</v>
+        <v>0.244</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3776</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.1568</v>
+        <v>4.9744</v>
       </c>
       <c r="E13" t="n">
-        <v>2.5164</v>
+        <v>2.116</v>
       </c>
       <c r="F13" t="n">
-        <v>2.6404</v>
+        <v>2.8585</v>
       </c>
       <c r="G13" t="n">
         <v>3.0795</v>
@@ -1468,13 +1468,13 @@
         <v>1.5523</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2429</v>
+        <v>0.0606</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4262</v>
+        <v>0.0258</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1832</v>
+        <v>0.0348</v>
       </c>
       <c r="V13" t="n">
         <v>0.2821</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. LORENZO  NEGRETE</t>
+          <t>B. GUEYE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.6052</v>
+        <v>3.2828</v>
       </c>
       <c r="E14" t="n">
-        <v>2.9646</v>
+        <v>1.9725</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6405</v>
+        <v>1.3103</v>
       </c>
       <c r="G14" t="n">
-        <v>3.5777</v>
+        <v>3.9909</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8288</v>
+        <v>2.4065</v>
       </c>
       <c r="I14" t="n">
-        <v>2.7489</v>
+        <v>1.5843</v>
       </c>
       <c r="J14" t="n">
-        <v>3.6577</v>
+        <v>3.0589</v>
       </c>
       <c r="K14" t="n">
-        <v>1.1534</v>
+        <v>2.9371</v>
       </c>
       <c r="L14" t="n">
-        <v>2.5043</v>
+        <v>0.1218</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.08</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3246</v>
+        <v>-0.5306</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2447</v>
+        <v>1.4626</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.7761</v>
+        <v>1.7463</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.1344</v>
+        <v>-0.194</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3582</v>
+        <v>1.9403</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1335</v>
+        <v>-0.6185</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5473</v>
+        <v>-0.5625</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5862000000000001</v>
+        <v>-0.0561</v>
       </c>
       <c r="V14" t="n">
+        <v>-1.8358</v>
+      </c>
+      <c r="W14" t="n">
         <v>-0.3299</v>
       </c>
-      <c r="W14" t="n">
-        <v>0.894</v>
-      </c>
       <c r="X14" t="n">
-        <v>-1.2239</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B. GUEYE</t>
+          <t>D. LORENZO  NEGRETE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.3195</v>
+        <v>2.9139</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1727</v>
+        <v>2.4641</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1467</v>
+        <v>0.4498</v>
       </c>
       <c r="G15" t="n">
-        <v>3.9909</v>
+        <v>3.5777</v>
       </c>
       <c r="H15" t="n">
-        <v>2.4065</v>
+        <v>0.8288</v>
       </c>
       <c r="I15" t="n">
-        <v>1.5843</v>
+        <v>2.7489</v>
       </c>
       <c r="J15" t="n">
-        <v>3.0589</v>
+        <v>3.6577</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9371</v>
+        <v>1.1534</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1218</v>
+        <v>2.5043</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9320000000000001</v>
+        <v>-0.08</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5306</v>
+        <v>-0.3246</v>
       </c>
       <c r="O15" t="n">
-        <v>1.4626</v>
+        <v>0.2447</v>
       </c>
       <c r="P15" t="n">
-        <v>1.7463</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.194</v>
+        <v>-2.1344</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9403</v>
+        <v>1.3582</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5819</v>
+        <v>0.4422</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3623</v>
+        <v>0.0468</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2196</v>
+        <v>0.3954</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.8358</v>
+        <v>-0.3299</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.3299</v>
+        <v>0.894</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.506</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. GACIC</t>
+          <t>V. ALONSO PASCUAL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2844</v>
+        <v>2.4179</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.8047</v>
+        <v>0.4543</v>
       </c>
       <c r="F16" t="n">
-        <v>4.0891</v>
+        <v>1.9636</v>
       </c>
       <c r="G16" t="n">
-        <v>1.8012</v>
+        <v>0.0447</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.9944</v>
+        <v>-0.6566</v>
       </c>
       <c r="I16" t="n">
-        <v>2.7956</v>
+        <v>0.7013</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7524999999999999</v>
+        <v>-0.098</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.2646</v>
+        <v>-0.0041</v>
       </c>
       <c r="L16" t="n">
-        <v>2.0171</v>
+        <v>-0.0939</v>
       </c>
       <c r="M16" t="n">
-        <v>1.0487</v>
+        <v>0.1427</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2702</v>
+        <v>-0.6525</v>
       </c>
       <c r="O16" t="n">
-        <v>0.7785</v>
+        <v>0.7952</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.5821</v>
+        <v>0.9702</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.1344</v>
+        <v>-0.9702</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5523</v>
+        <v>1.9403</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0653</v>
+        <v>-0.6671</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4229</v>
+        <v>-0.5476</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4882</v>
+        <v>-0.1194</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>2.0701</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.0701</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>V. ALONSO PASCUAL</t>
+          <t>I. GARCIA BENITO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.2539</v>
+        <v>1.9492</v>
       </c>
       <c r="E17" t="n">
-        <v>0.154</v>
+        <v>1.2791</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0999</v>
+        <v>0.6701</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0447</v>
+        <v>1.813</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.6566</v>
+        <v>0.421</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7013</v>
+        <v>1.392</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.098</v>
+        <v>1.2791</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.0041</v>
+        <v>0.0206</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.0939</v>
+        <v>1.2585</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1427</v>
+        <v>0.5339</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6525</v>
+        <v>0.4004</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7952</v>
+        <v>0.1335</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9702</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9403</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8310999999999999</v>
+        <v>0.1363</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8479</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0168</v>
+        <v>0.1363</v>
       </c>
       <c r="V17" t="n">
-        <v>2.0701</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.0701</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. GARCIA BENITO</t>
+          <t>S. ABOUBACAR HIMA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.8675</v>
+        <v>1.8466</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2791</v>
+        <v>1.2623</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5884</v>
+        <v>0.5843</v>
       </c>
       <c r="G18" t="n">
-        <v>1.813</v>
+        <v>1.8189</v>
       </c>
       <c r="H18" t="n">
-        <v>0.421</v>
+        <v>1.5225</v>
       </c>
       <c r="I18" t="n">
-        <v>1.392</v>
+        <v>0.2964</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2791</v>
+        <v>2.2037</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0206</v>
+        <v>1.3512</v>
       </c>
       <c r="L18" t="n">
-        <v>1.2585</v>
+        <v>0.8525</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5339</v>
+        <v>-0.3848</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4004</v>
+        <v>0.1714</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1335</v>
+        <v>-0.5561</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-0.194</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>0.7761</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0545</v>
+        <v>0.2695</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.0765</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0545</v>
+        <v>0.1929</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.0478</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.0478</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. ABOUBACAR HIMA</t>
+          <t>S. GACIC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.4551</v>
+        <v>1.776</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7618</v>
+        <v>-1.6045</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6933</v>
+        <v>3.3805</v>
       </c>
       <c r="G19" t="n">
-        <v>1.8189</v>
+        <v>1.8012</v>
       </c>
       <c r="H19" t="n">
-        <v>1.5225</v>
+        <v>-0.9944</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2964</v>
+        <v>2.7956</v>
       </c>
       <c r="J19" t="n">
-        <v>2.2037</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>1.3512</v>
+        <v>-1.2646</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8525</v>
+        <v>2.0171</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3848</v>
+        <v>1.0487</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1714</v>
+        <v>0.2702</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5561</v>
+        <v>0.7785</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.194</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9702</v>
+        <v>-2.1344</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7761</v>
+        <v>1.5523</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.122</v>
+        <v>0.5569</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.424</v>
+        <v>-0.2227</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3019</v>
+        <v>0.7795</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.0478</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.0478</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1493</v>
+        <v>0.2583</v>
       </c>
       <c r="E20" t="n">
         <v>0.0212</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1281</v>
+        <v>0.2371</v>
       </c>
       <c r="G20" t="n">
         <v>0.2706</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1214</v>
+        <v>-0.0123</v>
       </c>
       <c r="T20" t="n">
         <v>-0.0606</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0608</v>
+        <v>0.0482</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4734</v>
+        <v>-0.4189</v>
       </c>
       <c r="E21" t="n">
         <v>0.0412</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5145999999999999</v>
+        <v>-0.4601</v>
       </c>
       <c r="G21" t="n">
         <v>-0.3763</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.09710000000000001</v>
+        <v>-0.0426</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.09710000000000001</v>
+        <v>-0.0426</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.7371</v>
+        <v>-3.301</v>
       </c>
       <c r="E22" t="n">
         <v>-3.0181</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.719</v>
+        <v>-0.2829</v>
       </c>
       <c r="G22" t="n">
         <v>-2.5528</v>
@@ -2170,13 +2170,13 @@
         <v>2.3284</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.4545</v>
+        <v>-1.0184</v>
       </c>
       <c r="T22" t="n">
         <v>-0.544</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.9105</v>
+        <v>-0.4744</v>
       </c>
       <c r="V22" t="n">
         <v>-0.894</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>21.4172</v>
+        <v>21.4171</v>
       </c>
       <c r="E23" t="n">
-        <v>8.140699999999999</v>
+        <v>8.140700000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>13.2763</v>
+        <v>13.2765</v>
       </c>
       <c r="G23" t="n">
         <v>17.5197</v>
@@ -2248,7 +2248,7 @@
         <v>13.5823</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7907999999999998</v>
+        <v>-0.7905</v>
       </c>
       <c r="T23" t="n">
         <v>-1.9294</v>
